--- a/salidas/empresas/HPQ.xlsx
+++ b/salidas/empresas/HPQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>8.42396068572998</v>
+        <v>8.42396354675293</v>
       </c>
       <c r="C2" t="n">
         <v>14.15985488891602</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.864344596862793</v>
+        <v>8.864345550537109</v>
       </c>
       <c r="C3" t="n">
         <v>14.90009117126465</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>8.910264015197754</v>
+        <v>8.910265922546387</v>
       </c>
       <c r="C4" t="n">
         <v>14.94096279144287</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>8.793807983398438</v>
+        <v>8.79380989074707</v>
       </c>
       <c r="C5" t="n">
         <v>14.74568557739258</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>8.602843284606934</v>
+        <v>8.602842330932617</v>
       </c>
       <c r="C7" t="n">
         <v>14.38692092895508</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>8.665298461914062</v>
+        <v>8.665302276611328</v>
       </c>
       <c r="C8" t="n">
         <v>14.49137115478516</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>9.928030014038086</v>
+        <v>9.92802619934082</v>
       </c>
       <c r="C9" t="n">
         <v>16.60308837890625</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>9.985413551330566</v>
+        <v>9.985410690307617</v>
       </c>
       <c r="C10" t="n">
         <v>16.66212463378906</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>10.54333019256592</v>
+        <v>10.5433349609375</v>
       </c>
       <c r="C11" t="n">
         <v>17.59309768676758</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>10.73928546905518</v>
+        <v>10.73928451538086</v>
       </c>
       <c r="C12" t="n">
         <v>17.92007255554199</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.23279190063477</v>
+        <v>11.23278999328613</v>
       </c>
       <c r="C13" t="n">
         <v>18.70572280883789</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>11.80274772644043</v>
+        <v>11.80274486541748</v>
       </c>
       <c r="C14" t="n">
         <v>19.65485954284668</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.73100471496582</v>
+        <v>10.73100662231445</v>
       </c>
       <c r="C15" t="n">
         <v>17.8701171875</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>10.96831798553467</v>
+        <v>10.96832084655762</v>
       </c>
       <c r="C16" t="n">
         <v>18.22888374328613</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>12.49034023284912</v>
+        <v>12.49033355712891</v>
       </c>
       <c r="C18" t="n">
         <v>20.75840187072754</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>12.21382999420166</v>
+        <v>12.21383380889893</v>
       </c>
       <c r="C19" t="n">
         <v>20.26339721679688</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.59979343414307</v>
+        <v>12.59979724884033</v>
       </c>
       <c r="C20" t="n">
         <v>20.90372467041016</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>13.50857734680176</v>
+        <v>13.50857830047607</v>
       </c>
       <c r="C21" t="n">
         <v>22.41144371032715</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>13.65137958526611</v>
+        <v>13.6513729095459</v>
       </c>
       <c r="C22" t="n">
         <v>22.61126136779785</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.16957092285156</v>
+        <v>14.16957664489746</v>
       </c>
       <c r="C23" t="n">
         <v>23.46957206726074</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>14.02699756622314</v>
+        <v>14.0269947052002</v>
       </c>
       <c r="C24" t="n">
         <v>23.23342323303223</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>13.86195087432861</v>
+        <v>13.86194896697998</v>
       </c>
       <c r="C25" t="n">
         <v>22.92461395263672</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>12.00563526153564</v>
+        <v>12.0056324005127</v>
       </c>
       <c r="C26" t="n">
         <v>19.85467720031738</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>13.11777877807617</v>
+        <v>13.11778450012207</v>
       </c>
       <c r="C27" t="n">
         <v>21.69391441345215</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>12.9447021484375</v>
+        <v>12.9446964263916</v>
       </c>
       <c r="C30" t="n">
         <v>21.37148094177246</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>12.1812162399292</v>
+        <v>12.18121433258057</v>
       </c>
       <c r="C31" t="n">
         <v>20.07720375061035</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>12.34377956390381</v>
+        <v>12.34377288818359</v>
       </c>
       <c r="C32" t="n">
         <v>20.34514045715332</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>12.92789745330811</v>
+        <v>12.92790508270264</v>
       </c>
       <c r="C33" t="n">
         <v>21.30790138244629</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>10.56611442565918</v>
+        <v>10.56611633300781</v>
       </c>
       <c r="C35" t="n">
         <v>17.38419532775879</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.738052368164062</v>
+        <v>9.73805046081543</v>
       </c>
       <c r="C36" t="n">
         <v>16.02179718017578</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.03916072845459</v>
+        <v>10.03916168212891</v>
       </c>
       <c r="C37" t="n">
         <v>16.48047256469727</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>9.613139152526855</v>
+        <v>9.613142013549805</v>
       </c>
       <c r="C38" t="n">
         <v>15.78110790252686</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.03077507019043</v>
+        <v>8.030777931213379</v>
       </c>
       <c r="C39" t="n">
         <v>13.18346977233887</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.895362854003906</v>
+        <v>8.895363807678223</v>
       </c>
       <c r="C40" t="n">
         <v>14.55949115753174</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.983006477355957</v>
+        <v>9.983005523681641</v>
       </c>
       <c r="C41" t="n">
         <v>16.33969116210938</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.53075122833252</v>
+        <v>9.53074836730957</v>
       </c>
       <c r="C42" t="n">
         <v>15.59945487976074</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.74684524536133</v>
+        <v>10.74683952331543</v>
       </c>
       <c r="C43" t="n">
         <v>17.55222511291504</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.03979778289795</v>
+        <v>12.03980159759521</v>
       </c>
       <c r="C44" t="n">
         <v>19.66394233703613</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>12.48191070556641</v>
+        <v>12.48191165924072</v>
       </c>
       <c r="C45" t="n">
         <v>20.38601303100586</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.14981746673584</v>
+        <v>13.14981555938721</v>
       </c>
       <c r="C46" t="n">
         <v>21.43959999084473</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.21945667266846</v>
+        <v>13.21945953369141</v>
       </c>
       <c r="C47" t="n">
         <v>21.55313491821289</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>13.66512012481689</v>
+        <v>13.66511344909668</v>
       </c>
       <c r="C48" t="n">
         <v>22.27974510192871</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.37050724029541</v>
+        <v>14.37051200866699</v>
       </c>
       <c r="C49" t="n">
         <v>23.39237022399902</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>13.13181972503662</v>
+        <v>13.13181400299072</v>
       </c>
       <c r="C50" t="n">
         <v>21.37602233886719</v>
@@ -1443,7 +1455,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>14.85073566436768</v>
+        <v>14.85072994232178</v>
       </c>
       <c r="C52" t="n">
         <v>24.13714790344238</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>14.52102947235107</v>
+        <v>14.52102565765381</v>
       </c>
       <c r="C53" t="n">
         <v>23.60127258300781</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.85572719573975</v>
+        <v>12.85573577880859</v>
       </c>
       <c r="C54" t="n">
         <v>20.8946418762207</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>12.11347389221191</v>
+        <v>12.11347579956055</v>
       </c>
       <c r="C55" t="n">
         <v>19.65485954284668</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.88596153259277</v>
+        <v>12.88596248626709</v>
       </c>
       <c r="C56" t="n">
         <v>20.90826416015625</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.76162433624268</v>
+        <v>10.76162719726562</v>
       </c>
       <c r="C57" t="n">
         <v>17.46139907836914</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>11.79947471618652</v>
+        <v>11.79946708679199</v>
       </c>
       <c r="C58" t="n">
         <v>19.1053581237793</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>11.79105663299561</v>
+        <v>11.79105186462402</v>
       </c>
       <c r="C59" t="n">
         <v>19.09173583984375</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.7602014541626</v>
+        <v>11.76020812988281</v>
       </c>
       <c r="C60" t="n">
         <v>19.04178047180176</v>
@@ -1693,11 +1705,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>11.83008861541748</v>
+        <v>11.83009243011475</v>
       </c>
       <c r="C61" t="n">
         <v>19.11898231506348</v>
@@ -1722,11 +1734,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>12.83887958526611</v>
+        <v>12.83888244628906</v>
       </c>
       <c r="C62" t="n">
         <v>20.74931907653809</v>
@@ -1751,11 +1763,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.2600212097168</v>
+        <v>12.26002311706543</v>
       </c>
       <c r="C63" t="n">
         <v>19.81380653381348</v>
@@ -1780,11 +1792,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.53466892242432</v>
+        <v>11.53466987609863</v>
       </c>
       <c r="C64" t="n">
         <v>18.60581207275391</v>
@@ -1809,7 +1821,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1838,11 +1850,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.52394390106201</v>
+        <v>10.52394771575928</v>
       </c>
       <c r="C66" t="n">
         <v>16.97547721862793</v>
@@ -1867,11 +1879,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.28304481506348</v>
+        <v>10.28304576873779</v>
       </c>
       <c r="C67" t="n">
         <v>16.53042793273926</v>
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>9.935565948486328</v>
+        <v>9.935568809509277</v>
       </c>
       <c r="C68" t="n">
         <v>15.97184371948242</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>7.353506088256836</v>
+        <v>7.353506565093994</v>
       </c>
       <c r="C69" t="n">
         <v>11.82107162475586</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>6.375932693481445</v>
+        <v>6.375932216644287</v>
       </c>
       <c r="C70" t="n">
         <v>10.19527721405029</v>
@@ -1983,11 +1995,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.557397842407227</v>
+        <v>7.557399749755859</v>
       </c>
       <c r="C71" t="n">
         <v>12.08446884155273</v>
@@ -2012,11 +2024,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.937964916229248</v>
+        <v>7.937963485717773</v>
       </c>
       <c r="C72" t="n">
         <v>12.69300556182861</v>
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>7.347594738006592</v>
+        <v>7.347594261169434</v>
       </c>
       <c r="C73" t="n">
         <v>11.69845581054688</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>7.98081111907959</v>
+        <v>7.980809688568115</v>
       </c>
       <c r="C74" t="n">
         <v>12.70662975311279</v>
@@ -2099,7 +2111,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2128,11 +2140,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>6.830997467041016</v>
+        <v>6.830995082855225</v>
       </c>
       <c r="C76" t="n">
         <v>10.82198047637939</v>
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>7.097585678100586</v>
+        <v>7.097584247589111</v>
       </c>
       <c r="C77" t="n">
         <v>11.24432277679443</v>
@@ -2186,11 +2198,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>6.501343250274658</v>
+        <v>6.501340389251709</v>
       </c>
       <c r="C78" t="n">
         <v>10.29972839355469</v>
@@ -2215,11 +2227,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>5.798948764801025</v>
+        <v>5.798951625823975</v>
       </c>
       <c r="C79" t="n">
         <v>9.132607460021973</v>
@@ -2244,11 +2256,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>5.259711742401123</v>
+        <v>5.259713172912598</v>
       </c>
       <c r="C80" t="n">
         <v>8.283378601074219</v>
@@ -2273,7 +2285,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>4.957006454467773</v>
+        <v>4.95700740814209</v>
       </c>
       <c r="C82" t="n">
         <v>7.747501850128174</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>4.024301052093506</v>
+        <v>4.024299621582031</v>
       </c>
       <c r="C83" t="n">
         <v>6.289737224578857</v>
@@ -2356,11 +2368,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>3.774416446685791</v>
+        <v>3.774415731430054</v>
       </c>
       <c r="C84" t="n">
         <v>5.899182796478271</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>4.180109024047852</v>
+        <v>4.18010950088501</v>
       </c>
       <c r="C85" t="n">
         <v>6.471389770507812</v>
@@ -2410,7 +2422,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2437,11 +2449,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>5.907886505126953</v>
+        <v>5.907887935638428</v>
       </c>
       <c r="C87" t="n">
         <v>9.146230697631836</v>
@@ -2464,11 +2476,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>7.037479877471924</v>
+        <v>7.037482738494873</v>
       </c>
       <c r="C88" t="n">
         <v>10.8265209197998</v>
@@ -2491,11 +2503,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.081049919128418</v>
+        <v>6.081048488616943</v>
       </c>
       <c r="C89" t="n">
         <v>9.355132102966309</v>
@@ -2518,11 +2530,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>7.208697319030762</v>
+        <v>7.208698272705078</v>
       </c>
       <c r="C90" t="n">
         <v>11.08991813659668</v>
@@ -2545,11 +2557,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>7.363910675048828</v>
+        <v>7.363914012908936</v>
       </c>
       <c r="C91" t="n">
         <v>11.26248931884766</v>
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>7.625209808349609</v>
+        <v>7.625210285186768</v>
       </c>
       <c r="C92" t="n">
         <v>11.66212463378906</v>
@@ -2599,11 +2611,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>6.633456230163574</v>
+        <v>6.633458137512207</v>
       </c>
       <c r="C93" t="n">
         <v>10.1453218460083</v>
@@ -2626,11 +2638,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>6.273169040679932</v>
+        <v>6.27316951751709</v>
       </c>
       <c r="C94" t="n">
         <v>9.532242774963379</v>
@@ -2653,11 +2665,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>7.283332824707031</v>
+        <v>7.283333301544189</v>
       </c>
       <c r="C95" t="n">
         <v>11.06721210479736</v>
@@ -2680,11 +2692,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>8.173951148986816</v>
+        <v>8.173952102661133</v>
       </c>
       <c r="C96" t="n">
         <v>12.42052745819092</v>
@@ -2707,11 +2719,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>8.406240463256836</v>
+        <v>8.406237602233887</v>
       </c>
       <c r="C97" t="n">
         <v>12.70662975311279</v>
@@ -2736,11 +2748,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>8.712685585021973</v>
+        <v>8.71268367767334</v>
       </c>
       <c r="C98" t="n">
         <v>13.16984558105469</v>
@@ -2765,11 +2777,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>8.977071762084961</v>
+        <v>8.977068901062012</v>
       </c>
       <c r="C99" t="n">
         <v>13.56948184967041</v>
@@ -2794,11 +2806,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>9.768842697143555</v>
+        <v>9.768839836120605</v>
       </c>
       <c r="C100" t="n">
         <v>14.6957311630249</v>
@@ -2823,11 +2835,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>9.980159759521484</v>
+        <v>9.980156898498535</v>
       </c>
       <c r="C101" t="n">
         <v>15.01362419128418</v>
@@ -2852,11 +2864,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>10.1129846572876</v>
+        <v>10.11298656463623</v>
       </c>
       <c r="C102" t="n">
         <v>15.21344184875488</v>
@@ -2881,11 +2893,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>10.21562194824219</v>
+        <v>10.21562480926514</v>
       </c>
       <c r="C103" t="n">
         <v>15.29518604278564</v>
@@ -2910,11 +2922,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>10.80102062225342</v>
+        <v>10.80102252960205</v>
       </c>
       <c r="C104" t="n">
         <v>16.17166137695312</v>
@@ -2939,11 +2951,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>11.52594184875488</v>
+        <v>11.52594089508057</v>
       </c>
       <c r="C105" t="n">
         <v>17.25703811645508</v>
@@ -2968,11 +2980,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>10.80455780029297</v>
+        <v>10.80455875396729</v>
       </c>
       <c r="C106" t="n">
         <v>16.10808372497559</v>
@@ -2997,11 +3009,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>10.92944622039795</v>
+        <v>10.9294490814209</v>
       </c>
       <c r="C107" t="n">
         <v>16.29427719116211</v>
@@ -3026,11 +3038,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>11.89811515808105</v>
+        <v>11.89811038970947</v>
       </c>
       <c r="C108" t="n">
         <v>17.7384204864502</v>
@@ -3055,11 +3067,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>12.27369785308838</v>
+        <v>12.27370071411133</v>
       </c>
       <c r="C109" t="n">
         <v>18.22434234619141</v>
@@ -3084,11 +3096,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>11.0503044128418</v>
+        <v>11.05030345916748</v>
       </c>
       <c r="C110" t="n">
         <v>16.40781021118164</v>
@@ -3113,7 +3125,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3142,11 +3154,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>9.576420783996582</v>
+        <v>9.576418876647949</v>
       </c>
       <c r="C112" t="n">
         <v>14.15077209472656</v>
@@ -3171,11 +3183,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>10.13268756866455</v>
+        <v>10.1326847076416</v>
       </c>
       <c r="C113" t="n">
         <v>14.97275161743164</v>
@@ -3200,11 +3212,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>10.26483821868896</v>
+        <v>10.26484107971191</v>
       </c>
       <c r="C114" t="n">
         <v>15.16802883148193</v>
@@ -3229,11 +3241,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>9.272561073303223</v>
+        <v>9.272558212280273</v>
       </c>
       <c r="C115" t="n">
         <v>13.62852001190186</v>
@@ -3258,11 +3270,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>9.430144309997559</v>
+        <v>9.430142402648926</v>
       </c>
       <c r="C116" t="n">
         <v>13.86012744903564</v>
@@ -3287,11 +3299,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>8.670042991638184</v>
+        <v>8.6700439453125</v>
       </c>
       <c r="C117" t="n">
         <v>12.74296092987061</v>
@@ -3316,11 +3328,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.962862968444824</v>
+        <v>7.962858200073242</v>
       </c>
       <c r="C118" t="n">
         <v>11.63033580780029</v>
@@ -3345,11 +3357,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>8.382608413696289</v>
+        <v>8.382613182067871</v>
       </c>
       <c r="C119" t="n">
         <v>12.24341487884521</v>
@@ -3374,11 +3386,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.585673332214355</v>
+        <v>8.585671424865723</v>
       </c>
       <c r="C120" t="n">
         <v>12.53999996185303</v>
@@ -3403,11 +3415,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>8.188826560974121</v>
+        <v>8.18882942199707</v>
       </c>
       <c r="C121" t="n">
         <v>11.84000015258789</v>
@@ -3432,11 +3444,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.715667724609375</v>
+        <v>6.715671539306641</v>
       </c>
       <c r="C122" t="n">
         <v>9.710000038146973</v>
@@ -3461,11 +3473,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>7.393460750579834</v>
+        <v>7.393460273742676</v>
       </c>
       <c r="C123" t="n">
         <v>10.6899995803833</v>
@@ -3490,7 +3502,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3519,11 +3531,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>8.581406593322754</v>
+        <v>8.581405639648438</v>
       </c>
       <c r="C125" t="n">
         <v>12.27000045776367</v>
@@ -3548,7 +3560,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3577,11 +3589,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>8.858599662780762</v>
+        <v>8.858603477478027</v>
       </c>
       <c r="C127" t="n">
         <v>12.55000019073486</v>
@@ -3606,11 +3618,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>9.889162063598633</v>
+        <v>9.889163970947266</v>
       </c>
       <c r="C128" t="n">
         <v>14.01000022888184</v>
@@ -3635,7 +3647,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3664,11 +3676,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>11.05954456329346</v>
+        <v>11.05954551696777</v>
       </c>
       <c r="C130" t="n">
         <v>15.52999973297119</v>
@@ -3693,11 +3705,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>10.31891918182373</v>
+        <v>10.31892013549805</v>
       </c>
       <c r="C131" t="n">
         <v>14.48999977111816</v>
@@ -3722,11 +3734,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>10.966965675354</v>
+        <v>10.96696758270264</v>
       </c>
       <c r="C132" t="n">
         <v>15.39999961853027</v>
@@ -3751,11 +3763,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>10.65799903869629</v>
+        <v>10.65799713134766</v>
       </c>
       <c r="C133" t="n">
         <v>14.84000015258789</v>
@@ -3780,11 +3792,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>10.8088207244873</v>
+        <v>10.80881977081299</v>
       </c>
       <c r="C134" t="n">
         <v>15.05000019073486</v>
@@ -3809,11 +3821,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>12.4750280380249</v>
+        <v>12.47502994537354</v>
       </c>
       <c r="C135" t="n">
         <v>17.3700008392334</v>
@@ -3838,11 +3850,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>12.94050884246826</v>
+        <v>12.940505027771</v>
       </c>
       <c r="C136" t="n">
         <v>17.8799991607666</v>
@@ -3867,11 +3879,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>13.62082004547119</v>
+        <v>13.62082481384277</v>
       </c>
       <c r="C137" t="n">
         <v>18.81999969482422</v>
@@ -3896,11 +3908,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>13.57739353179932</v>
+        <v>13.5773983001709</v>
       </c>
       <c r="C138" t="n">
         <v>18.76000022888184</v>
@@ -3925,11 +3937,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>12.74624919891357</v>
+        <v>12.74624729156494</v>
       </c>
       <c r="C139" t="n">
         <v>17.47999954223633</v>
@@ -3954,11 +3966,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>13.92753601074219</v>
+        <v>13.9275369644165</v>
       </c>
       <c r="C140" t="n">
         <v>19.10000038146973</v>
@@ -3983,11 +3995,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>13.9129524230957</v>
+        <v>13.91295433044434</v>
       </c>
       <c r="C141" t="n">
         <v>19.07999992370605</v>
@@ -4012,11 +4024,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>14.65552806854248</v>
+        <v>14.6555290222168</v>
       </c>
       <c r="C142" t="n">
         <v>19.95999908447266</v>
@@ -4041,11 +4053,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>15.8229808807373</v>
+        <v>15.82297706604004</v>
       </c>
       <c r="C143" t="n">
         <v>21.54999923706055</v>
@@ -4070,11 +4082,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>15.74954700469971</v>
+        <v>15.74955368041992</v>
       </c>
       <c r="C144" t="n">
         <v>21.45000076293945</v>
@@ -4099,11 +4111,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>15.52781867980957</v>
+        <v>15.52781963348389</v>
       </c>
       <c r="C145" t="n">
         <v>21.01000022888184</v>
@@ -4128,11 +4140,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>17.23506164550781</v>
+        <v>17.23506736755371</v>
       </c>
       <c r="C146" t="n">
         <v>23.31999969482422</v>
@@ -4157,7 +4169,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4186,7 +4198,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4215,11 +4227,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>15.97575664520264</v>
+        <v>15.97575950622559</v>
       </c>
       <c r="C149" t="n">
         <v>21.48999977111816</v>
@@ -4244,7 +4256,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4273,11 +4285,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>16.96606254577637</v>
+        <v>16.966064453125</v>
       </c>
       <c r="C151" t="n">
         <v>22.69000053405762</v>
@@ -4302,11 +4314,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>17.2576789855957</v>
+        <v>17.2576732635498</v>
       </c>
       <c r="C152" t="n">
         <v>23.07999992370605</v>
@@ -4331,11 +4343,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>18.4316234588623</v>
+        <v>18.43161964416504</v>
       </c>
       <c r="C153" t="n">
         <v>24.64999961853027</v>
@@ -4360,7 +4372,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4389,11 +4401,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>18.15263748168945</v>
+        <v>18.15264129638672</v>
       </c>
       <c r="C155" t="n">
         <v>24.13999938964844</v>
@@ -4418,11 +4430,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>17.29538726806641</v>
+        <v>17.29538917541504</v>
       </c>
       <c r="C156" t="n">
         <v>23</v>
@@ -4447,11 +4459,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>15.49532318115234</v>
+        <v>15.49531936645508</v>
       </c>
       <c r="C157" t="n">
         <v>20.45999908447266</v>
@@ -4476,11 +4488,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>16.68435859680176</v>
+        <v>16.68435668945312</v>
       </c>
       <c r="C158" t="n">
         <v>22.03000068664551</v>
@@ -4505,11 +4517,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>14.94245719909668</v>
+        <v>14.94245624542236</v>
       </c>
       <c r="C159" t="n">
         <v>19.72999954223633</v>
@@ -4534,11 +4546,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>14.83995628356934</v>
+        <v>14.83995914459229</v>
       </c>
       <c r="C160" t="n">
         <v>19.43000030517578</v>
@@ -4563,11 +4575,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>15.23712158203125</v>
+        <v>15.2371187210083</v>
       </c>
       <c r="C161" t="n">
         <v>19.95000076293945</v>
@@ -4592,11 +4604,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>14.26713371276855</v>
+        <v>14.26713943481445</v>
       </c>
       <c r="C162" t="n">
         <v>18.68000030517578</v>
@@ -4621,7 +4633,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4650,11 +4662,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>16.19999885559082</v>
+        <v>16.20000457763672</v>
       </c>
       <c r="C164" t="n">
         <v>21.04000091552734</v>
@@ -4679,11 +4691,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>14.08260631561279</v>
+        <v>14.08261203765869</v>
       </c>
       <c r="C165" t="n">
         <v>18.29000091552734</v>
@@ -4708,11 +4720,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>14.69133567810059</v>
+        <v>14.69133377075195</v>
       </c>
       <c r="C166" t="n">
         <v>18.92000007629395</v>
@@ -4737,11 +4749,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>13.48776531219482</v>
+        <v>13.48776340484619</v>
       </c>
       <c r="C167" t="n">
         <v>17.3700008392334</v>
@@ -4766,7 +4778,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4795,11 +4807,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>16.09541702270508</v>
+        <v>16.09541320800781</v>
       </c>
       <c r="C169" t="n">
         <v>20.54999923706055</v>
@@ -4824,11 +4836,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>16.6985034942627</v>
+        <v>16.69849967956543</v>
       </c>
       <c r="C170" t="n">
         <v>21.31999969482422</v>
@@ -4853,7 +4865,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4882,11 +4894,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>13.72430038452148</v>
+        <v>13.72430515289307</v>
       </c>
       <c r="C172" t="n">
         <v>17.36000061035156</v>
@@ -4911,11 +4923,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>12.26174831390381</v>
+        <v>12.26174736022949</v>
       </c>
       <c r="C173" t="n">
         <v>15.51000022888184</v>
@@ -4940,11 +4952,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>11.96923828125</v>
+        <v>11.96923732757568</v>
       </c>
       <c r="C174" t="n">
         <v>15.14000034332275</v>
@@ -4969,11 +4981,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>13.91442108154297</v>
+        <v>13.91442203521729</v>
       </c>
       <c r="C175" t="n">
         <v>17.43000030517578</v>
@@ -4998,11 +5010,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>14.03417015075684</v>
+        <v>14.0341682434082</v>
       </c>
       <c r="C176" t="n">
         <v>17.57999992370605</v>
@@ -5027,11 +5039,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>15.60682392120361</v>
+        <v>15.60682010650635</v>
       </c>
       <c r="C177" t="n">
         <v>19.54999923706055</v>
@@ -5056,11 +5068,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>15.29980278015137</v>
+        <v>15.29980754852295</v>
       </c>
       <c r="C178" t="n">
         <v>18.98999977111816</v>
@@ -5085,11 +5097,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>14.46995639801025</v>
+        <v>14.46995544433594</v>
       </c>
       <c r="C179" t="n">
         <v>17.95999908447266</v>
@@ -5114,11 +5126,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>17.66849327087402</v>
+        <v>17.66849517822266</v>
       </c>
       <c r="C180" t="n">
         <v>21.93000030517578</v>
@@ -5143,11 +5155,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>19.97524070739746</v>
+        <v>19.97524452209473</v>
       </c>
       <c r="C181" t="n">
         <v>24.59000015258789</v>
@@ -5172,11 +5184,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>19.77216720581055</v>
+        <v>19.77215957641602</v>
       </c>
       <c r="C182" t="n">
         <v>24.34000015258789</v>
@@ -5201,11 +5213,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>23.53326225280762</v>
+        <v>23.53325653076172</v>
       </c>
       <c r="C183" t="n">
         <v>28.96999931335449</v>
@@ -5230,11 +5242,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>25.95851516723633</v>
+        <v>25.95851707458496</v>
       </c>
       <c r="C184" t="n">
         <v>31.75</v>
@@ -5259,11 +5271,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>27.88803100585938</v>
+        <v>27.88803672790527</v>
       </c>
       <c r="C185" t="n">
         <v>34.11000061035156</v>
@@ -5288,11 +5300,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>23.8981876373291</v>
+        <v>23.89818572998047</v>
       </c>
       <c r="C186" t="n">
         <v>29.22999954223633</v>
@@ -5317,7 +5329,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5346,11 +5358,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>23.75470161437988</v>
+        <v>23.75469779968262</v>
       </c>
       <c r="C188" t="n">
         <v>28.8700008392334</v>
@@ -5375,11 +5387,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>24.47055053710938</v>
+        <v>24.47054862976074</v>
       </c>
       <c r="C189" t="n">
         <v>29.73999977111816</v>
@@ -5404,11 +5416,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>22.65946578979492</v>
+        <v>22.65946769714355</v>
       </c>
       <c r="C190" t="n">
         <v>27.36000061035156</v>
@@ -5433,7 +5445,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5462,11 +5474,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>29.21878051757812</v>
+        <v>29.21878242492676</v>
       </c>
       <c r="C192" t="n">
         <v>35.27999877929688</v>
@@ -5491,11 +5503,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>31.41081237792969</v>
+        <v>31.41080284118652</v>
       </c>
       <c r="C193" t="n">
         <v>37.66999816894531</v>
@@ -5520,7 +5532,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5549,11 +5561,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>28.65079307556152</v>
+        <v>28.65079689025879</v>
       </c>
       <c r="C195" t="n">
         <v>34.36000061035156</v>
@@ -5578,11 +5590,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>30.48214340209961</v>
+        <v>30.48214721679688</v>
       </c>
       <c r="C196" t="n">
         <v>36.29999923706055</v>
@@ -5607,11 +5619,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>30.75926208496094</v>
+        <v>30.75925827026367</v>
       </c>
       <c r="C197" t="n">
         <v>36.63000106811523</v>
@@ -5636,11 +5648,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>32.61505126953125</v>
+        <v>32.61505889892578</v>
       </c>
       <c r="C198" t="n">
         <v>38.84000015258789</v>
@@ -5665,7 +5677,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5694,7 +5706,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5723,11 +5735,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>24.26208877563477</v>
+        <v>24.26208686828613</v>
       </c>
       <c r="C201" t="n">
         <v>28.70999908447266</v>
@@ -5752,11 +5764,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>21.24555587768555</v>
+        <v>21.24555206298828</v>
       </c>
       <c r="C202" t="n">
         <v>24.92000007629395</v>
@@ -5781,11 +5793,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>23.54744148254395</v>
+        <v>23.54743957519531</v>
       </c>
       <c r="C203" t="n">
         <v>27.6200008392334</v>
@@ -5810,11 +5822,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>25.61061096191406</v>
+        <v>25.61061668395996</v>
       </c>
       <c r="C204" t="n">
         <v>30.04000091552734</v>
@@ -5839,11 +5851,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>23.11753463745117</v>
+        <v>23.11753845214844</v>
       </c>
       <c r="C205" t="n">
         <v>26.8700008392334</v>
@@ -5868,11 +5880,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>25.07052612304688</v>
+        <v>25.07052040100098</v>
       </c>
       <c r="C206" t="n">
         <v>29.13999938964844</v>
@@ -5897,11 +5909,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>25.3974552154541</v>
+        <v>25.39745330810547</v>
       </c>
       <c r="C207" t="n">
         <v>29.52000045776367</v>
@@ -5926,11 +5938,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>25.48580741882324</v>
+        <v>25.48580551147461</v>
       </c>
       <c r="C208" t="n">
         <v>29.35000038146973</v>
@@ -5955,11 +5967,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>25.79841041564941</v>
+        <v>25.79840850830078</v>
       </c>
       <c r="C209" t="n">
         <v>29.70999908447266</v>
@@ -5984,11 +5996,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.23398590087891</v>
+        <v>25.23398399353027</v>
       </c>
       <c r="C210" t="n">
         <v>29.05999946594238</v>
@@ -6013,7 +6025,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6042,11 +6054,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>28.7560863494873</v>
+        <v>28.75608444213867</v>
       </c>
       <c r="C212" t="n">
         <v>32.83000183105469</v>
@@ -6071,11 +6083,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>26.02325248718262</v>
+        <v>26.02324485778809</v>
       </c>
       <c r="C213" t="n">
         <v>29.70999908447266</v>
@@ -6100,11 +6112,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>22.71293449401855</v>
+        <v>22.71293640136719</v>
       </c>
       <c r="C214" t="n">
         <v>25.70000076293945</v>
@@ -6129,7 +6141,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6158,7 +6170,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6187,11 +6199,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>26.83658218383789</v>
+        <v>26.83658027648926</v>
       </c>
       <c r="C217" t="n">
         <v>30.09000015258789</v>
@@ -6216,11 +6228,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>25.60579109191895</v>
+        <v>25.60579299926758</v>
       </c>
       <c r="C218" t="n">
         <v>28.70999908447266</v>
@@ -6245,7 +6257,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6274,7 +6286,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6303,11 +6315,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>25.2789134979248</v>
+        <v>25.27891159057617</v>
       </c>
       <c r="C221" t="n">
         <v>28.09000015258789</v>
@@ -6332,11 +6344,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>32.8472900390625</v>
+        <v>32.84728622436523</v>
       </c>
       <c r="C222" t="n">
         <v>36.5</v>
@@ -6361,7 +6373,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6390,11 +6402,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>32.72701263427734</v>
+        <v>32.72701644897461</v>
       </c>
       <c r="C224" t="n">
         <v>36.09000015258789</v>
@@ -6419,11 +6431,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>32.80863571166992</v>
+        <v>32.80862808227539</v>
       </c>
       <c r="C225" t="n">
         <v>36.18000030517578</v>
@@ -6448,11 +6460,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>32.79796600341797</v>
+        <v>32.7979736328125</v>
       </c>
       <c r="C226" t="n">
         <v>35.86999893188477</v>
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6506,11 +6518,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>32.39566040039062</v>
+        <v>32.39565277099609</v>
       </c>
       <c r="C228" t="n">
         <v>35.43000030517578</v>
@@ -6535,7 +6547,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6564,11 +6576,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>29.96443748474121</v>
+        <v>29.96443557739258</v>
       </c>
       <c r="C230" t="n">
         <v>32.5</v>
@@ -6593,11 +6605,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>28.46160507202148</v>
+        <v>28.46160697937012</v>
       </c>
       <c r="C231" t="n">
         <v>30.8700008392334</v>
@@ -6622,7 +6634,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6651,7 +6663,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6680,11 +6692,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>23.19155311584473</v>
+        <v>23.19155120849609</v>
       </c>
       <c r="C234" t="n">
         <v>24.89999961853027</v>
@@ -6709,11 +6721,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>23.04227447509766</v>
+        <v>23.04227256774902</v>
       </c>
       <c r="C235" t="n">
         <v>24.45999908447266</v>
@@ -6738,7 +6750,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6767,7 +6779,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6796,7 +6808,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6825,11 +6837,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>26.32823371887207</v>
+        <v>26.32823181152344</v>
       </c>
       <c r="C239" t="n">
         <v>27.67000007629395</v>
@@ -6854,7 +6866,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6883,7 +6895,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6912,7 +6924,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6941,7 +6953,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6970,7 +6982,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6999,7 +7011,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7028,7 +7040,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7057,7 +7069,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7086,7 +7098,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7115,7 +7127,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7144,32 +7156,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>32.15999984741211</v>
+        <v>31.13999938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>32.15999984741211</v>
+        <v>31.13999938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>273812800</v>
+        <v>285708900</v>
       </c>
       <c r="E250" t="n">
         <v>2.619999999999999</v>
       </c>
       <c r="F250" t="n">
-        <v>12.2748091020657</v>
+        <v>11.8854959502475</v>
       </c>
       <c r="G250" t="n">
         <v>901790969</v>
       </c>
       <c r="H250" t="n">
-        <v>29001597425.43762</v>
+        <v>28081770224.25047</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3036322267716123</v>
+        <v>0.3168238647552923</v>
       </c>
     </row>
   </sheetData>
@@ -7201,75 +7213,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39569</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39660</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40064</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7305,13 +7317,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39753</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40248</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7347,13 +7359,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40337</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7389,13 +7401,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40064</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7431,13 +7443,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40248</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7473,13 +7485,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40337</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7515,13 +7527,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40430</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7557,13 +7569,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40527</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7590,7 +7602,7 @@
       <c r="I9" t="n">
         <v>1.67574931880109</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40527</v>
       </c>
       <c r="K9" t="n">
@@ -7603,13 +7615,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7636,7 +7648,7 @@
       <c r="I10" t="n">
         <v>1.784741144414169</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="K10" t="n">
@@ -7649,13 +7661,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40702</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7682,7 +7694,7 @@
       <c r="I11" t="n">
         <v>1.848319709355132</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40702</v>
       </c>
       <c r="K11" t="n">
@@ -7695,13 +7707,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40795</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7728,7 +7740,7 @@
       <c r="I12" t="n">
         <v>1.930063578564941</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40795</v>
       </c>
       <c r="K12" t="n">
@@ -7741,13 +7753,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40891</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7774,7 +7786,7 @@
       <c r="I13" t="n">
         <v>1.50772025431426</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40891</v>
       </c>
       <c r="K13" t="n">
@@ -7787,13 +7799,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40980</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7820,7 +7832,7 @@
       <c r="I14" t="n">
         <v>1.307901907356948</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40980</v>
       </c>
       <c r="K14" t="n">
@@ -7833,13 +7845,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41068</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7866,7 +7878,7 @@
       <c r="I15" t="n">
         <v>1.194368755676658</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41068</v>
       </c>
       <c r="K15" t="n">
@@ -7879,13 +7891,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41162</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7912,7 +7924,7 @@
       <c r="I16" t="n">
         <v>-1.267029972752044</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41162</v>
       </c>
       <c r="K16" t="n">
@@ -7925,13 +7937,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41270</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7958,7 +7970,7 @@
       <c r="I17" t="n">
         <v>-2.910990009082652</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41270</v>
       </c>
       <c r="K17" t="n">
@@ -7971,13 +7983,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41344</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8004,7 +8016,7 @@
       <c r="I18" t="n">
         <v>-2.956403269754769</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41344</v>
       </c>
       <c r="K18" t="n">
@@ -8017,13 +8029,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41431</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8050,7 +8062,7 @@
       <c r="I19" t="n">
         <v>-3.069936421435059</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41431</v>
       </c>
       <c r="K19" t="n">
@@ -8063,13 +8075,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41526</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8096,7 +8108,7 @@
       <c r="I20" t="n">
         <v>-0.7084468664850135</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41526</v>
       </c>
       <c r="K20" t="n">
@@ -8109,13 +8121,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41638</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8142,7 +8154,7 @@
       <c r="I21" t="n">
         <v>1.189827429609446</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41638</v>
       </c>
       <c r="K21" t="n">
@@ -8155,13 +8167,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41709</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8188,7 +8200,7 @@
       <c r="I22" t="n">
         <v>1.239782016348774</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41709</v>
       </c>
       <c r="K22" t="n">
@@ -8201,13 +8213,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41799</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8234,7 +8246,7 @@
       <c r="I23" t="n">
         <v>1.289736603088102</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41799</v>
       </c>
       <c r="K23" t="n">
@@ -8247,13 +8259,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8280,7 +8292,7 @@
       <c r="I24" t="n">
         <v>1.203451407811081</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="K24" t="n">
@@ -8293,13 +8305,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8326,7 +8338,7 @@
       <c r="I25" t="n">
         <v>1.189827429609446</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="K25" t="n">
@@ -8339,13 +8351,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8372,7 +8384,7 @@
       <c r="I26" t="n">
         <v>1.185286103542234</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="K26" t="n">
@@ -8385,13 +8397,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42163</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8418,7 +8430,7 @@
       <c r="I27" t="n">
         <v>1.135331516802907</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42163</v>
       </c>
       <c r="K27" t="n">
@@ -8431,13 +8443,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8464,7 +8476,7 @@
       <c r="I28" t="n">
         <v>1.112624886466848</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="K28" t="n">
@@ -8477,13 +8489,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42354</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8510,7 +8522,7 @@
       <c r="I29" t="n">
         <v>2.48</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42354</v>
       </c>
       <c r="K29" t="n">
@@ -8523,13 +8535,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8556,7 +8568,7 @@
       <c r="I30" t="n">
         <v>2.478483197093551</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="K30" t="n">
@@ -8569,13 +8581,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8602,7 +8614,7 @@
       <c r="I31" t="n">
         <v>2.588710263396912</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="K31" t="n">
@@ -8615,13 +8627,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8648,7 +8660,7 @@
       <c r="I32" t="n">
         <v>2.825267938237965</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="K32" t="n">
@@ -8661,13 +8673,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8694,7 +8706,7 @@
       <c r="I33" t="n">
         <v>1.43</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="K33" t="n">
@@ -8707,13 +8719,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42796</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8740,7 +8752,7 @@
       <c r="I34" t="n">
         <v>1.46</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42796</v>
       </c>
       <c r="K34" t="n">
@@ -8753,13 +8765,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8786,7 +8798,7 @@
       <c r="I35" t="n">
         <v>1.43</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="K35" t="n">
@@ -8799,13 +8811,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8832,7 +8844,7 @@
       <c r="I36" t="n">
         <v>1.39</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="K36" t="n">
@@ -8845,13 +8857,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8878,7 +8890,7 @@
       <c r="I37" t="n">
         <v>1.48</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="K37" t="n">
@@ -8891,13 +8903,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8924,7 +8936,7 @@
       <c r="I38" t="n">
         <v>2.28</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K38" t="n">
@@ -8937,13 +8949,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8970,7 +8982,7 @@
       <c r="I39" t="n">
         <v>2.59</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="K39" t="n">
@@ -8983,13 +8995,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43340</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9016,7 +9028,7 @@
       <c r="I40" t="n">
         <v>2.72</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43340</v>
       </c>
       <c r="K40" t="n">
@@ -9029,13 +9041,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9062,7 +9074,7 @@
       <c r="I41" t="n">
         <v>3.26</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="K41" t="n">
@@ -9075,13 +9087,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43529</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9108,7 +9120,7 @@
       <c r="I42" t="n">
         <v>2.609999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43529</v>
       </c>
       <c r="K42" t="n">
@@ -9121,13 +9133,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9154,7 +9166,7 @@
       <c r="I43" t="n">
         <v>2.48</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="K43" t="n">
@@ -9167,13 +9179,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9200,7 +9212,7 @@
       <c r="I44" t="n">
         <v>2.719999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="K44" t="n">
@@ -9213,13 +9225,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43811</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9246,7 +9258,7 @@
       <c r="I45" t="n">
         <v>2.069999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43811</v>
       </c>
       <c r="K45" t="n">
@@ -9259,13 +9271,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43895</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9292,7 +9304,7 @@
       <c r="I46" t="n">
         <v>2.02</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43895</v>
       </c>
       <c r="K46" t="n">
@@ -9305,13 +9317,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9338,7 +9350,7 @@
       <c r="I47" t="n">
         <v>2.039999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="K47" t="n">
@@ -9351,13 +9363,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9384,7 +9396,7 @@
       <c r="I48" t="n">
         <v>1.78</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="K48" t="n">
@@ -9397,13 +9409,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44175</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9430,7 +9442,7 @@
       <c r="I49" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44175</v>
       </c>
       <c r="K49" t="n">
@@ -9443,13 +9455,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9476,7 +9488,7 @@
       <c r="I50" t="n">
         <v>2.37</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="K50" t="n">
@@ -9489,13 +9501,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9522,7 +9534,7 @@
       <c r="I51" t="n">
         <v>2.819999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="K51" t="n">
@@ -9535,13 +9547,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9568,7 +9580,7 @@
       <c r="I52" t="n">
         <v>3.22</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="K52" t="n">
@@ -9581,13 +9593,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44539</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9614,7 +9626,7 @@
       <c r="I53" t="n">
         <v>5.329999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44539</v>
       </c>
       <c r="K53" t="n">
@@ -9627,13 +9639,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44627</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9660,7 +9672,7 @@
       <c r="I54" t="n">
         <v>5.489999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44627</v>
       </c>
       <c r="K54" t="n">
@@ -9673,13 +9685,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9706,7 +9718,7 @@
       <c r="I55" t="n">
         <v>5.449999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="K55" t="n">
@@ -9719,13 +9731,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9752,7 +9764,7 @@
       <c r="I56" t="n">
         <v>5.609999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="K56" t="n">
@@ -9765,13 +9777,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44901</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9798,7 +9810,7 @@
       <c r="I57" t="n">
         <v>3.049999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44901</v>
       </c>
       <c r="K57" t="n">
@@ -9811,13 +9823,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9844,7 +9856,7 @@
       <c r="I58" t="n">
         <v>2.549999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="K58" t="n">
@@ -9857,13 +9869,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9890,7 +9902,7 @@
       <c r="I59" t="n">
         <v>2.679999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="K59" t="n">
@@ -9903,13 +9915,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9936,7 +9948,7 @@
       <c r="I60" t="n">
         <v>2.359999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="K60" t="n">
@@ -9949,13 +9961,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9982,7 +9994,7 @@
       <c r="I61" t="n">
         <v>3.259999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="K61" t="n">
@@ -9995,13 +10007,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10028,7 +10040,7 @@
       <c r="I62" t="n">
         <v>3.389999999999998</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K62" t="n">
@@ -10041,13 +10053,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10074,7 +10086,7 @@
       <c r="I63" t="n">
         <v>2.929999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="K63" t="n">
@@ -10087,13 +10099,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10120,7 +10132,7 @@
       <c r="I64" t="n">
         <v>2.819999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="K64" t="n">
@@ -10133,13 +10145,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10166,7 +10178,7 @@
       <c r="I65" t="n">
         <v>2.809999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="K65" t="n">
@@ -10179,13 +10191,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10212,7 +10224,7 @@
       <c r="I66" t="n">
         <v>2.779999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="K66" t="n">
@@ -10225,13 +10237,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10258,7 +10270,7 @@
       <c r="I67" t="n">
         <v>2.589999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="K67" t="n">
@@ -10271,13 +10283,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10304,7 +10316,7 @@
       <c r="I68" t="n">
         <v>2.739999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="K68" t="n">
@@ -10317,13 +10329,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10350,7 +10362,7 @@
       <c r="I69" t="n">
         <v>2.649999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="K69" t="n">
@@ -10363,13 +10375,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10396,7 +10408,7 @@
       <c r="I70" t="n">
         <v>2.639999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K70" t="n">
@@ -10409,13 +10421,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10442,7 +10454,7 @@
       <c r="I71" t="n">
         <v>2.709999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="K71" t="n">
@@ -10455,13 +10467,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10488,7 +10500,7 @@
       <c r="I72" t="n">
         <v>2.619999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="K72" t="n">
@@ -10525,52 +10537,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40064</v>
       </c>
       <c r="C2" t="n">
@@ -10599,10 +10611,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40164</v>
       </c>
       <c r="C3" t="n">
@@ -10631,10 +10643,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40248</v>
       </c>
       <c r="C4" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40337</v>
       </c>
       <c r="C5" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40430</v>
       </c>
       <c r="C6" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40527</v>
       </c>
       <c r="C7" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40613</v>
       </c>
       <c r="C8" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40702</v>
       </c>
       <c r="C9" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40795</v>
       </c>
       <c r="C10" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40891</v>
       </c>
       <c r="C11" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40980</v>
       </c>
       <c r="C12" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41068</v>
       </c>
       <c r="C13" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41162</v>
       </c>
       <c r="C14" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41270</v>
       </c>
       <c r="C15" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41344</v>
       </c>
       <c r="C16" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41431</v>
       </c>
       <c r="C17" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41526</v>
       </c>
       <c r="C18" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41638</v>
       </c>
       <c r="C19" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41709</v>
       </c>
       <c r="C20" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41799</v>
       </c>
       <c r="C21" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41891</v>
       </c>
       <c r="C22" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="C23" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="C24" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42163</v>
       </c>
       <c r="C25" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42255</v>
       </c>
       <c r="C26" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42354</v>
       </c>
       <c r="C27" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42432</v>
       </c>
       <c r="C28" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="C29" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C30" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42719</v>
       </c>
       <c r="C31" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42796</v>
       </c>
       <c r="C32" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="C33" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="C34" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C35" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43256</v>
       </c>
       <c r="C36" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43340</v>
       </c>
       <c r="C37" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43447</v>
       </c>
       <c r="C38" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43529</v>
       </c>
       <c r="C39" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43615</v>
       </c>
       <c r="C40" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43706</v>
       </c>
       <c r="C41" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43811</v>
       </c>
       <c r="C42" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C43" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="C44" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="C45" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44175</v>
       </c>
       <c r="C46" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="C47" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="C48" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="C49" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44539</v>
       </c>
       <c r="C50" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44627</v>
       </c>
       <c r="C51" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="C52" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="C53" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44901</v>
       </c>
       <c r="C54" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="C55" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="C56" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45180</v>
       </c>
       <c r="C57" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45278</v>
       </c>
       <c r="C58" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C59" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45442</v>
       </c>
       <c r="C60" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="C61" t="n">
@@ -12487,10 +12499,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45628</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="C62" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45712</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="C63" t="n">
@@ -12551,10 +12563,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45799</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45806</v>
       </c>
       <c r="C64" t="n">
@@ -12583,10 +12595,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45891</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45897</v>
       </c>
       <c r="C65" t="n">
@@ -12615,10 +12627,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="C66" t="n">
@@ -12647,10 +12659,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C67" t="n">
@@ -12679,10 +12691,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46170</v>
       </c>
       <c r="C68" t="n">
@@ -12711,10 +12723,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46253</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46261</v>
       </c>
       <c r="C69" t="n">
@@ -12761,12 +12773,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/HPQ.xlsx
+++ b/salidas/empresas/HPQ.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>8.42396354675293</v>
+        <v>8.423964500427246</v>
       </c>
       <c r="C2" t="n">
         <v>14.15985488891602</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>8.864345550537109</v>
+        <v>8.864341735839844</v>
       </c>
       <c r="C3" t="n">
         <v>14.90009117126465</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>8.910265922546387</v>
+        <v>8.910262107849121</v>
       </c>
       <c r="C4" t="n">
         <v>14.94096279144287</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>8.79380989074707</v>
+        <v>8.793808937072754</v>
       </c>
       <c r="C5" t="n">
         <v>14.74568557739258</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>8.769433975219727</v>
+        <v>8.769432067871094</v>
       </c>
       <c r="C6" t="n">
         <v>14.70481395721436</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>8.602842330932617</v>
+        <v>8.602843284606934</v>
       </c>
       <c r="C7" t="n">
         <v>14.38692092895508</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>8.665302276611328</v>
+        <v>8.665298461914062</v>
       </c>
       <c r="C8" t="n">
         <v>14.49137115478516</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>9.92802619934082</v>
+        <v>9.928025245666504</v>
       </c>
       <c r="C9" t="n">
         <v>16.60308837890625</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>9.985410690307617</v>
+        <v>9.985413551330566</v>
       </c>
       <c r="C10" t="n">
         <v>16.66212463378906</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>10.5433349609375</v>
+        <v>10.54333400726318</v>
       </c>
       <c r="C11" t="n">
         <v>17.59309768676758</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>10.73928451538086</v>
+        <v>10.73928737640381</v>
       </c>
       <c r="C12" t="n">
         <v>17.92007255554199</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>11.23278999328613</v>
+        <v>11.23278522491455</v>
       </c>
       <c r="C13" t="n">
         <v>18.70572280883789</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>11.80274486541748</v>
+        <v>11.8027400970459</v>
       </c>
       <c r="C14" t="n">
         <v>19.65485954284668</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>10.73100662231445</v>
+        <v>10.73100852966309</v>
       </c>
       <c r="C15" t="n">
         <v>17.8701171875</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>11.51482391357422</v>
+        <v>11.51482963562012</v>
       </c>
       <c r="C17" t="n">
         <v>19.13714790344238</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>12.59979724884033</v>
+        <v>12.59979438781738</v>
       </c>
       <c r="C20" t="n">
         <v>20.90372467041016</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>13.50857830047607</v>
+        <v>13.50857543945312</v>
       </c>
       <c r="C21" t="n">
         <v>22.41144371032715</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>13.6513729095459</v>
+        <v>13.65137195587158</v>
       </c>
       <c r="C22" t="n">
         <v>22.61126136779785</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>14.16957664489746</v>
+        <v>14.16957092285156</v>
       </c>
       <c r="C23" t="n">
         <v>23.46957206726074</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>14.0269947052002</v>
+        <v>14.02700614929199</v>
       </c>
       <c r="C24" t="n">
         <v>23.23342323303223</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>13.86194896697998</v>
+        <v>13.86195278167725</v>
       </c>
       <c r="C25" t="n">
         <v>22.92461395263672</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>13.11778450012207</v>
+        <v>13.11776733398438</v>
       </c>
       <c r="C27" t="n">
         <v>21.69391441345215</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>12.55959987640381</v>
+        <v>12.55960273742676</v>
       </c>
       <c r="C28" t="n">
         <v>20.73569488525391</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>12.9446964263916</v>
+        <v>12.94469738006592</v>
       </c>
       <c r="C30" t="n">
         <v>21.37148094177246</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>12.34377288818359</v>
+        <v>12.34377479553223</v>
       </c>
       <c r="C32" t="n">
         <v>20.34514045715332</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>12.92790508270264</v>
+        <v>12.92790412902832</v>
       </c>
       <c r="C33" t="n">
         <v>21.30790138244629</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>12.76325130462646</v>
+        <v>12.76325416564941</v>
       </c>
       <c r="C34" t="n">
         <v>20.99909210205078</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>9.73805046081543</v>
+        <v>9.738052368164062</v>
       </c>
       <c r="C36" t="n">
         <v>16.02179718017578</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.03916168212891</v>
+        <v>10.03916454315186</v>
       </c>
       <c r="C37" t="n">
         <v>16.48047256469727</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>9.613142013549805</v>
+        <v>9.613137245178223</v>
       </c>
       <c r="C38" t="n">
         <v>15.78110790252686</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.030777931213379</v>
+        <v>8.030776023864746</v>
       </c>
       <c r="C39" t="n">
         <v>13.18346977233887</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.895363807678223</v>
+        <v>8.895362854003906</v>
       </c>
       <c r="C40" t="n">
         <v>14.55949115753174</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>9.53074836730957</v>
+        <v>9.530746459960938</v>
       </c>
       <c r="C42" t="n">
         <v>15.59945487976074</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.74683952331543</v>
+        <v>10.74684524536133</v>
       </c>
       <c r="C43" t="n">
         <v>17.55222511291504</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.03980159759521</v>
+        <v>12.0398063659668</v>
       </c>
       <c r="C44" t="n">
         <v>19.66394233703613</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.14981555938721</v>
+        <v>13.14981651306152</v>
       </c>
       <c r="C46" t="n">
         <v>21.43959999084473</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.21945953369141</v>
+        <v>13.21945667266846</v>
       </c>
       <c r="C47" t="n">
         <v>21.55313491821289</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>14.37051200866699</v>
+        <v>14.37050151824951</v>
       </c>
       <c r="C49" t="n">
         <v>23.39237022399902</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.85573577880859</v>
+        <v>12.8557300567627</v>
       </c>
       <c r="C54" t="n">
         <v>20.8946418762207</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.88596248626709</v>
+        <v>12.88595867156982</v>
       </c>
       <c r="C56" t="n">
         <v>20.90826416015625</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.76162719726562</v>
+        <v>10.76162147521973</v>
       </c>
       <c r="C57" t="n">
         <v>17.46139907836914</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>11.79946708679199</v>
+        <v>11.79947090148926</v>
       </c>
       <c r="C58" t="n">
         <v>19.1053581237793</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>11.79105186462402</v>
+        <v>11.79105854034424</v>
       </c>
       <c r="C59" t="n">
         <v>19.09173583984375</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>11.76020812988281</v>
+        <v>11.76020908355713</v>
       </c>
       <c r="C60" t="n">
         <v>19.04178047180176</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>11.83009243011475</v>
+        <v>11.83008766174316</v>
       </c>
       <c r="C61" t="n">
         <v>19.11898231506348</v>
@@ -1767,7 +1767,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>12.26002311706543</v>
+        <v>12.26002502441406</v>
       </c>
       <c r="C63" t="n">
         <v>19.81380653381348</v>
@@ -1796,7 +1796,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>11.53466987609863</v>
+        <v>11.53467273712158</v>
       </c>
       <c r="C64" t="n">
         <v>18.60581207275391</v>
@@ -1825,7 +1825,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>11.36575031280518</v>
+        <v>11.36575508117676</v>
       </c>
       <c r="C65" t="n">
         <v>18.33333206176758</v>
@@ -1854,7 +1854,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>10.52394771575928</v>
+        <v>10.52395248413086</v>
       </c>
       <c r="C66" t="n">
         <v>16.97547721862793</v>
@@ -1883,7 +1883,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>10.28304576873779</v>
+        <v>10.28304195404053</v>
       </c>
       <c r="C67" t="n">
         <v>16.53042793273926</v>
@@ -1970,7 +1970,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>6.375932216644287</v>
+        <v>6.375931262969971</v>
       </c>
       <c r="C70" t="n">
         <v>10.19527721405029</v>
@@ -1999,7 +1999,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>7.557399749755859</v>
+        <v>7.557395458221436</v>
       </c>
       <c r="C71" t="n">
         <v>12.08446884155273</v>
@@ -2028,7 +2028,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>7.937963485717773</v>
+        <v>7.937967300415039</v>
       </c>
       <c r="C72" t="n">
         <v>12.69300556182861</v>
@@ -2057,7 +2057,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>7.347594261169434</v>
+        <v>7.347596168518066</v>
       </c>
       <c r="C73" t="n">
         <v>11.69845581054688</v>
@@ -2086,7 +2086,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>7.980809688568115</v>
+        <v>7.980812549591064</v>
       </c>
       <c r="C74" t="n">
         <v>12.70662975311279</v>
@@ -2115,7 +2115,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>7.219240665435791</v>
+        <v>7.219241619110107</v>
       </c>
       <c r="C75" t="n">
         <v>11.49409580230713</v>
@@ -2144,7 +2144,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>6.830995082855225</v>
+        <v>6.830997943878174</v>
       </c>
       <c r="C76" t="n">
         <v>10.82198047637939</v>
@@ -2173,7 +2173,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>7.097584247589111</v>
+        <v>7.097588539123535</v>
       </c>
       <c r="C77" t="n">
         <v>11.24432277679443</v>
@@ -2202,7 +2202,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>6.501340389251709</v>
+        <v>6.5013427734375</v>
       </c>
       <c r="C78" t="n">
         <v>10.29972839355469</v>
@@ -2231,7 +2231,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>5.798951625823975</v>
+        <v>5.7989501953125</v>
       </c>
       <c r="C79" t="n">
         <v>9.132607460021973</v>
@@ -2260,7 +2260,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>5.259713172912598</v>
+        <v>5.259713649749756</v>
       </c>
       <c r="C80" t="n">
         <v>8.283378601074219</v>
@@ -2289,7 +2289,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>4.86754035949707</v>
+        <v>4.867540836334229</v>
       </c>
       <c r="C81" t="n">
         <v>7.66575813293457</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>4.024299621582031</v>
+        <v>4.024300098419189</v>
       </c>
       <c r="C83" t="n">
         <v>6.289737224578857</v>
@@ -2372,7 +2372,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>3.774415731430054</v>
+        <v>3.774416446685791</v>
       </c>
       <c r="C84" t="n">
         <v>5.899182796478271</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>4.18010950088501</v>
+        <v>4.180107593536377</v>
       </c>
       <c r="C85" t="n">
         <v>6.471389770507812</v>
@@ -2453,7 +2453,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>5.907887935638428</v>
+        <v>5.90788459777832</v>
       </c>
       <c r="C87" t="n">
         <v>9.146230697631836</v>
@@ -2480,7 +2480,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>7.037482738494873</v>
+        <v>7.037485599517822</v>
       </c>
       <c r="C88" t="n">
         <v>10.8265209197998</v>
@@ -2507,7 +2507,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.081048488616943</v>
+        <v>6.081045627593994</v>
       </c>
       <c r="C89" t="n">
         <v>9.355132102966309</v>
@@ -2534,7 +2534,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>7.208698272705078</v>
+        <v>7.208699226379395</v>
       </c>
       <c r="C90" t="n">
         <v>11.08991813659668</v>
@@ -2561,7 +2561,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>7.363914012908936</v>
+        <v>7.363908767700195</v>
       </c>
       <c r="C91" t="n">
         <v>11.26248931884766</v>
@@ -2588,7 +2588,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>7.625210285186768</v>
+        <v>7.625207901000977</v>
       </c>
       <c r="C92" t="n">
         <v>11.66212463378906</v>
@@ -2615,7 +2615,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>6.633458137512207</v>
+        <v>6.633458614349365</v>
       </c>
       <c r="C93" t="n">
         <v>10.1453218460083</v>
@@ -2642,7 +2642,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>6.27316951751709</v>
+        <v>6.273169040679932</v>
       </c>
       <c r="C94" t="n">
         <v>9.532242774963379</v>
@@ -2669,7 +2669,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>7.283333301544189</v>
+        <v>7.283336162567139</v>
       </c>
       <c r="C95" t="n">
         <v>11.06721210479736</v>
@@ -2696,7 +2696,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>8.173952102661133</v>
+        <v>8.173949241638184</v>
       </c>
       <c r="C96" t="n">
         <v>12.42052745819092</v>
@@ -2723,7 +2723,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>8.406237602233887</v>
+        <v>8.40623664855957</v>
       </c>
       <c r="C97" t="n">
         <v>12.70662975311279</v>
@@ -2752,7 +2752,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>8.71268367767334</v>
+        <v>8.712682723999023</v>
       </c>
       <c r="C98" t="n">
         <v>13.16984558105469</v>
@@ -2781,7 +2781,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>8.977068901062012</v>
+        <v>8.977070808410645</v>
       </c>
       <c r="C99" t="n">
         <v>13.56948184967041</v>
@@ -2810,7 +2810,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>9.768839836120605</v>
+        <v>9.768841743469238</v>
       </c>
       <c r="C100" t="n">
         <v>14.6957311630249</v>
@@ -2868,7 +2868,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>10.11298656463623</v>
+        <v>10.11298274993896</v>
       </c>
       <c r="C102" t="n">
         <v>15.21344184875488</v>
@@ -2897,7 +2897,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>10.21562480926514</v>
+        <v>10.21562385559082</v>
       </c>
       <c r="C103" t="n">
         <v>15.29518604278564</v>
@@ -2926,7 +2926,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>10.80102252960205</v>
+        <v>10.8010196685791</v>
       </c>
       <c r="C104" t="n">
         <v>16.17166137695312</v>
@@ -2955,7 +2955,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>11.52594089508057</v>
+        <v>11.5259428024292</v>
       </c>
       <c r="C105" t="n">
         <v>17.25703811645508</v>
@@ -2984,7 +2984,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>10.80455875396729</v>
+        <v>10.8045597076416</v>
       </c>
       <c r="C106" t="n">
         <v>16.10808372497559</v>
@@ -3013,7 +3013,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>10.9294490814209</v>
+        <v>10.92944717407227</v>
       </c>
       <c r="C107" t="n">
         <v>16.29427719116211</v>
@@ -3042,7 +3042,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>11.89811038970947</v>
+        <v>11.89811229705811</v>
       </c>
       <c r="C108" t="n">
         <v>17.7384204864502</v>
@@ -3071,7 +3071,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>12.27370071411133</v>
+        <v>12.27369689941406</v>
       </c>
       <c r="C109" t="n">
         <v>18.22434234619141</v>
@@ -3129,7 +3129,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>10.65576171875</v>
+        <v>10.65576267242432</v>
       </c>
       <c r="C111" t="n">
         <v>15.82198047637939</v>
@@ -3187,7 +3187,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>10.1326847076416</v>
+        <v>10.13268661499023</v>
       </c>
       <c r="C113" t="n">
         <v>14.97275161743164</v>
@@ -3216,7 +3216,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>10.26484107971191</v>
+        <v>10.26483917236328</v>
       </c>
       <c r="C114" t="n">
         <v>15.16802883148193</v>
@@ -3245,7 +3245,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>9.272558212280273</v>
+        <v>9.272560119628906</v>
       </c>
       <c r="C115" t="n">
         <v>13.62852001190186</v>
@@ -3274,7 +3274,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>9.430142402648926</v>
+        <v>9.430140495300293</v>
       </c>
       <c r="C116" t="n">
         <v>13.86012744903564</v>
@@ -3303,7 +3303,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>8.6700439453125</v>
+        <v>8.670045852661133</v>
       </c>
       <c r="C117" t="n">
         <v>12.74296092987061</v>
@@ -3332,7 +3332,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.962858200073242</v>
+        <v>7.962859153747559</v>
       </c>
       <c r="C118" t="n">
         <v>11.63033580780029</v>
@@ -3361,7 +3361,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>8.382613182067871</v>
+        <v>8.382611274719238</v>
       </c>
       <c r="C119" t="n">
         <v>12.24341487884521</v>
@@ -3390,7 +3390,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.585671424865723</v>
+        <v>8.585673332214355</v>
       </c>
       <c r="C120" t="n">
         <v>12.53999996185303</v>
@@ -3419,7 +3419,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>8.18882942199707</v>
+        <v>8.188830375671387</v>
       </c>
       <c r="C121" t="n">
         <v>11.84000015258789</v>
@@ -3448,7 +3448,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.715671539306641</v>
+        <v>6.715667724609375</v>
       </c>
       <c r="C122" t="n">
         <v>9.710000038146973</v>
@@ -3477,7 +3477,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>7.393460273742676</v>
+        <v>7.393458366394043</v>
       </c>
       <c r="C123" t="n">
         <v>10.6899995803833</v>
@@ -3506,7 +3506,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>8.616374015808105</v>
+        <v>8.616374969482422</v>
       </c>
       <c r="C124" t="n">
         <v>12.31999969482422</v>
@@ -3535,7 +3535,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>8.581405639648438</v>
+        <v>8.581408500671387</v>
       </c>
       <c r="C125" t="n">
         <v>12.27000045776367</v>
@@ -3564,7 +3564,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>9.357720375061035</v>
+        <v>9.357719421386719</v>
       </c>
       <c r="C126" t="n">
         <v>13.38000011444092</v>
@@ -3593,7 +3593,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>8.858603477478027</v>
+        <v>8.858599662780762</v>
       </c>
       <c r="C127" t="n">
         <v>12.55000019073486</v>
@@ -3622,7 +3622,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>9.889163970947266</v>
+        <v>9.889163017272949</v>
       </c>
       <c r="C128" t="n">
         <v>14.01000022888184</v>
@@ -3651,7 +3651,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>10.14327335357666</v>
+        <v>10.14327526092529</v>
       </c>
       <c r="C129" t="n">
         <v>14.36999988555908</v>
@@ -3709,7 +3709,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>10.31892013549805</v>
+        <v>10.31892108917236</v>
       </c>
       <c r="C131" t="n">
         <v>14.48999977111816</v>
@@ -3738,7 +3738,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>10.96696758270264</v>
+        <v>10.96696472167969</v>
       </c>
       <c r="C132" t="n">
         <v>15.39999961853027</v>
@@ -3767,7 +3767,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>10.65799713134766</v>
+        <v>10.65799903869629</v>
       </c>
       <c r="C133" t="n">
         <v>14.84000015258789</v>
@@ -3796,7 +3796,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>10.80881977081299</v>
+        <v>10.80881786346436</v>
       </c>
       <c r="C134" t="n">
         <v>15.05000019073486</v>
@@ -3825,7 +3825,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>12.47502994537354</v>
+        <v>12.47503089904785</v>
       </c>
       <c r="C135" t="n">
         <v>17.3700008392334</v>
@@ -3854,7 +3854,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>12.940505027771</v>
+        <v>12.94050693511963</v>
       </c>
       <c r="C136" t="n">
         <v>17.8799991607666</v>
@@ -3912,7 +3912,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>13.5773983001709</v>
+        <v>13.57739639282227</v>
       </c>
       <c r="C138" t="n">
         <v>18.76000022888184</v>
@@ -3941,7 +3941,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>12.74624729156494</v>
+        <v>12.74624919891357</v>
       </c>
       <c r="C139" t="n">
         <v>17.47999954223633</v>
@@ -4057,7 +4057,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>15.82297706604004</v>
+        <v>15.82298183441162</v>
       </c>
       <c r="C143" t="n">
         <v>21.54999923706055</v>
@@ -4086,7 +4086,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>15.74955368041992</v>
+        <v>15.74955558776855</v>
       </c>
       <c r="C144" t="n">
         <v>21.45000076293945</v>
@@ -4115,7 +4115,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>15.52781963348389</v>
+        <v>15.52781581878662</v>
       </c>
       <c r="C145" t="n">
         <v>21.01000022888184</v>
@@ -4144,7 +4144,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>17.23506736755371</v>
+        <v>17.23506355285645</v>
       </c>
       <c r="C146" t="n">
         <v>23.31999969482422</v>
@@ -4173,7 +4173,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>17.28679847717285</v>
+        <v>17.28680038452148</v>
       </c>
       <c r="C147" t="n">
         <v>23.38999938964844</v>
@@ -4202,7 +4202,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>16.2954216003418</v>
+        <v>16.29542541503906</v>
       </c>
       <c r="C148" t="n">
         <v>21.92000007629395</v>
@@ -4231,7 +4231,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>15.97575950622559</v>
+        <v>15.97575092315674</v>
       </c>
       <c r="C149" t="n">
         <v>21.48999977111816</v>
@@ -4260,7 +4260,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>16.37719345092773</v>
+        <v>16.377197265625</v>
       </c>
       <c r="C150" t="n">
         <v>22.03000068664551</v>
@@ -4289,7 +4289,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>16.966064453125</v>
+        <v>16.96606636047363</v>
       </c>
       <c r="C151" t="n">
         <v>22.69000053405762</v>
@@ -4318,7 +4318,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>17.2576732635498</v>
+        <v>17.25768089294434</v>
       </c>
       <c r="C152" t="n">
         <v>23.07999992370605</v>
@@ -4347,7 +4347,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>18.43161964416504</v>
+        <v>18.43161392211914</v>
       </c>
       <c r="C153" t="n">
         <v>24.64999961853027</v>
@@ -4405,7 +4405,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>18.15264129638672</v>
+        <v>18.15263938903809</v>
       </c>
       <c r="C155" t="n">
         <v>24.13999938964844</v>
@@ -4434,7 +4434,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>17.29538917541504</v>
+        <v>17.29538536071777</v>
       </c>
       <c r="C156" t="n">
         <v>23</v>
@@ -4463,7 +4463,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>15.49531936645508</v>
+        <v>15.49531745910645</v>
       </c>
       <c r="C157" t="n">
         <v>20.45999908447266</v>
@@ -4492,7 +4492,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>16.68435668945312</v>
+        <v>16.68435478210449</v>
       </c>
       <c r="C158" t="n">
         <v>22.03000068664551</v>
@@ -4521,7 +4521,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>14.94245624542236</v>
+        <v>14.94245529174805</v>
       </c>
       <c r="C159" t="n">
         <v>19.72999954223633</v>
@@ -4550,7 +4550,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>14.83995914459229</v>
+        <v>14.83995723724365</v>
       </c>
       <c r="C160" t="n">
         <v>19.43000030517578</v>
@@ -4579,7 +4579,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>15.2371187210083</v>
+        <v>15.23711585998535</v>
       </c>
       <c r="C161" t="n">
         <v>19.95000076293945</v>
@@ -4608,7 +4608,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>14.26713943481445</v>
+        <v>14.26713085174561</v>
       </c>
       <c r="C162" t="n">
         <v>18.68000030517578</v>
@@ -4637,7 +4637,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>16.00751686096191</v>
+        <v>16.00751113891602</v>
       </c>
       <c r="C163" t="n">
         <v>20.79000091552734</v>
@@ -4666,7 +4666,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>16.20000457763672</v>
+        <v>16.20000267028809</v>
       </c>
       <c r="C164" t="n">
         <v>21.04000091552734</v>
@@ -4695,7 +4695,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>14.08261203765869</v>
+        <v>14.08260631561279</v>
       </c>
       <c r="C165" t="n">
         <v>18.29000091552734</v>
@@ -4724,7 +4724,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>14.69133377075195</v>
+        <v>14.6913366317749</v>
       </c>
       <c r="C166" t="n">
         <v>18.92000007629395</v>
@@ -4753,7 +4753,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>13.48776340484619</v>
+        <v>13.48776721954346</v>
       </c>
       <c r="C167" t="n">
         <v>17.3700008392334</v>
@@ -4782,7 +4782,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>15.59207153320312</v>
+        <v>15.59207344055176</v>
       </c>
       <c r="C168" t="n">
         <v>20.07999992370605</v>
@@ -4811,7 +4811,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>16.09541320800781</v>
+        <v>16.09541893005371</v>
       </c>
       <c r="C169" t="n">
         <v>20.54999923706055</v>
@@ -4840,7 +4840,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>16.69849967956543</v>
+        <v>16.69850540161133</v>
       </c>
       <c r="C170" t="n">
         <v>21.31999969482422</v>
@@ -4869,7 +4869,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>16.28339195251465</v>
+        <v>16.28338813781738</v>
       </c>
       <c r="C171" t="n">
         <v>20.79000091552734</v>
@@ -4898,7 +4898,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>13.72430515289307</v>
+        <v>13.72430610656738</v>
       </c>
       <c r="C172" t="n">
         <v>17.36000061035156</v>
@@ -4927,7 +4927,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>12.26174736022949</v>
+        <v>12.26174926757812</v>
       </c>
       <c r="C173" t="n">
         <v>15.51000022888184</v>
@@ -4985,7 +4985,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>13.91442203521729</v>
+        <v>13.91442394256592</v>
       </c>
       <c r="C175" t="n">
         <v>17.43000030517578</v>
@@ -5014,7 +5014,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>14.0341682434082</v>
+        <v>14.03416442871094</v>
       </c>
       <c r="C176" t="n">
         <v>17.57999992370605</v>
@@ -5043,7 +5043,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>15.60682010650635</v>
+        <v>15.60682487487793</v>
       </c>
       <c r="C177" t="n">
         <v>19.54999923706055</v>
@@ -5072,7 +5072,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>15.29980754852295</v>
+        <v>15.2998046875</v>
       </c>
       <c r="C178" t="n">
         <v>18.98999977111816</v>
@@ -5101,7 +5101,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>14.46995544433594</v>
+        <v>14.4699592590332</v>
       </c>
       <c r="C179" t="n">
         <v>17.95999908447266</v>
@@ -5130,7 +5130,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>17.66849517822266</v>
+        <v>17.66849327087402</v>
       </c>
       <c r="C180" t="n">
         <v>21.93000030517578</v>
@@ -5188,7 +5188,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>19.77215957641602</v>
+        <v>19.77216148376465</v>
       </c>
       <c r="C182" t="n">
         <v>24.34000015258789</v>
@@ -5217,7 +5217,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>23.53325653076172</v>
+        <v>23.53325843811035</v>
       </c>
       <c r="C183" t="n">
         <v>28.96999931335449</v>
@@ -5246,7 +5246,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>25.95851707458496</v>
+        <v>25.95851135253906</v>
       </c>
       <c r="C184" t="n">
         <v>31.75</v>
@@ -5275,7 +5275,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>27.88803672790527</v>
+        <v>27.88803291320801</v>
       </c>
       <c r="C185" t="n">
         <v>34.11000061035156</v>
@@ -5304,7 +5304,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>23.89818572998047</v>
+        <v>23.89818382263184</v>
       </c>
       <c r="C186" t="n">
         <v>29.22999954223633</v>
@@ -5333,7 +5333,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>24.8408203125</v>
+        <v>24.84081840515137</v>
       </c>
       <c r="C187" t="n">
         <v>30.19000053405762</v>
@@ -5362,7 +5362,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>23.75469779968262</v>
+        <v>23.75470161437988</v>
       </c>
       <c r="C188" t="n">
         <v>28.8700008392334</v>
@@ -5391,7 +5391,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>24.47054862976074</v>
+        <v>24.47055244445801</v>
       </c>
       <c r="C189" t="n">
         <v>29.73999977111816</v>
@@ -5449,7 +5449,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>25.11920738220215</v>
+        <v>25.11921310424805</v>
       </c>
       <c r="C191" t="n">
         <v>30.32999992370605</v>
@@ -5478,7 +5478,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>29.21878242492676</v>
+        <v>29.21878051757812</v>
       </c>
       <c r="C192" t="n">
         <v>35.27999877929688</v>
@@ -5507,7 +5507,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>31.41080284118652</v>
+        <v>31.41080093383789</v>
       </c>
       <c r="C193" t="n">
         <v>37.66999816894531</v>
@@ -5536,7 +5536,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>30.62699699401855</v>
+        <v>30.62700080871582</v>
       </c>
       <c r="C194" t="n">
         <v>36.72999954223633</v>
@@ -5565,7 +5565,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>28.65079689025879</v>
+        <v>28.65080070495605</v>
       </c>
       <c r="C195" t="n">
         <v>34.36000061035156</v>
@@ -5623,7 +5623,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>30.75925827026367</v>
+        <v>30.7592601776123</v>
       </c>
       <c r="C197" t="n">
         <v>36.63000106811523</v>
@@ -5681,7 +5681,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.7015380859375</v>
+        <v>27.70153617858887</v>
       </c>
       <c r="C199" t="n">
         <v>32.77999877929688</v>
@@ -5710,7 +5710,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>28.21703338623047</v>
+        <v>28.2170352935791</v>
       </c>
       <c r="C200" t="n">
         <v>33.38999938964844</v>
@@ -5768,7 +5768,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>21.24555206298828</v>
+        <v>21.24555587768555</v>
       </c>
       <c r="C202" t="n">
         <v>24.92000007629395</v>
@@ -5826,7 +5826,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>25.61061668395996</v>
+        <v>25.61061859130859</v>
       </c>
       <c r="C204" t="n">
         <v>30.04000091552734</v>
@@ -5855,7 +5855,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>23.11753845214844</v>
+        <v>23.11753463745117</v>
       </c>
       <c r="C205" t="n">
         <v>26.8700008392334</v>
@@ -5884,7 +5884,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>25.07052040100098</v>
+        <v>25.07052230834961</v>
       </c>
       <c r="C206" t="n">
         <v>29.13999938964844</v>
@@ -5913,7 +5913,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>25.39745330810547</v>
+        <v>25.3974609375</v>
       </c>
       <c r="C207" t="n">
         <v>29.52000045776367</v>
@@ -5942,7 +5942,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>25.48580551147461</v>
+        <v>25.48579978942871</v>
       </c>
       <c r="C208" t="n">
         <v>29.35000038146973</v>
@@ -5971,7 +5971,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>25.79840850830078</v>
+        <v>25.79840469360352</v>
       </c>
       <c r="C209" t="n">
         <v>29.70999908447266</v>
@@ -6000,7 +6000,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.23398399353027</v>
+        <v>25.23398590087891</v>
       </c>
       <c r="C210" t="n">
         <v>29.05999946594238</v>
@@ -6029,7 +6029,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>26.8991527557373</v>
+        <v>26.89915657043457</v>
       </c>
       <c r="C211" t="n">
         <v>30.70999908447266</v>
@@ -6058,7 +6058,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>28.75608444213867</v>
+        <v>28.75608825683594</v>
       </c>
       <c r="C212" t="n">
         <v>32.83000183105469</v>
@@ -6145,7 +6145,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>23.26971054077148</v>
+        <v>23.26971244812012</v>
       </c>
       <c r="C215" t="n">
         <v>26.32999992370605</v>
@@ -6174,7 +6174,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>25.92986488342285</v>
+        <v>25.92986297607422</v>
       </c>
       <c r="C216" t="n">
         <v>29.34000015258789</v>
@@ -6203,7 +6203,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>26.83658027648926</v>
+        <v>26.83657836914062</v>
       </c>
       <c r="C217" t="n">
         <v>30.09000015258789</v>
@@ -6232,7 +6232,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>25.60579299926758</v>
+        <v>25.60579109191895</v>
       </c>
       <c r="C218" t="n">
         <v>28.70999908447266</v>
@@ -6261,7 +6261,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>25.26687812805176</v>
+        <v>25.26687622070312</v>
       </c>
       <c r="C219" t="n">
         <v>28.32999992370605</v>
@@ -6290,7 +6290,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>27.19575309753418</v>
+        <v>27.19575119018555</v>
       </c>
       <c r="C220" t="n">
         <v>30.21999931335449</v>
@@ -6319,7 +6319,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>25.27891159057617</v>
+        <v>25.2789134979248</v>
       </c>
       <c r="C221" t="n">
         <v>28.09000015258789</v>
@@ -6377,7 +6377,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>31.7567195892334</v>
+        <v>31.75671577453613</v>
       </c>
       <c r="C223" t="n">
         <v>35.02000045776367</v>
@@ -6406,7 +6406,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>32.72701644897461</v>
+        <v>32.72701263427734</v>
       </c>
       <c r="C224" t="n">
         <v>36.09000015258789</v>
@@ -6464,7 +6464,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>32.7979736328125</v>
+        <v>32.79796981811523</v>
       </c>
       <c r="C226" t="n">
         <v>35.86999893188477</v>
@@ -6493,7 +6493,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>32.47794342041016</v>
+        <v>32.47794723510742</v>
       </c>
       <c r="C227" t="n">
         <v>35.52000045776367</v>
@@ -6551,7 +6551,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>30.08429336547852</v>
+        <v>30.08429527282715</v>
       </c>
       <c r="C229" t="n">
         <v>32.63000106811523</v>
@@ -6580,7 +6580,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>29.96443557739258</v>
+        <v>29.96443367004395</v>
       </c>
       <c r="C230" t="n">
         <v>32.5</v>
@@ -6609,7 +6609,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>28.46160697937012</v>
+        <v>28.46160316467285</v>
       </c>
       <c r="C231" t="n">
         <v>30.8700008392334</v>
@@ -6696,7 +6696,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>23.19155120849609</v>
+        <v>23.19155502319336</v>
       </c>
       <c r="C234" t="n">
         <v>24.89999961853027</v>
@@ -6725,7 +6725,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>23.04227256774902</v>
+        <v>23.04227447509766</v>
       </c>
       <c r="C235" t="n">
         <v>24.45999908447266</v>
@@ -6754,7 +6754,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>23.3625659942627</v>
+        <v>23.36256790161133</v>
       </c>
       <c r="C236" t="n">
         <v>24.79999923706055</v>
@@ -6783,7 +6783,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>26.88579559326172</v>
+        <v>26.88579368591309</v>
       </c>
       <c r="C237" t="n">
         <v>28.54000091552734</v>
@@ -6870,7 +6870,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>23.23583030700684</v>
+        <v>23.2358283996582</v>
       </c>
       <c r="C240" t="n">
         <v>24.42000007629395</v>
